--- a/AAAGameData/Languages/French.xlsx
+++ b/AAAGameData/Languages/French.xlsx
@@ -55,66 +55,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
-  <si>
-    <t>BRAKE</t>
-  </si>
-  <si>
-    <t>Freins</t>
-  </si>
-  <si>
-    <t>ENGINE</t>
-  </si>
-  <si>
-    <t>Moteur</t>
-  </si>
-  <si>
-    <t>Failed</t>
-  </si>
-  <si>
-    <t>Le jeu a échoué</t>
-  </si>
-  <si>
-    <t>GameOverUIForm.Back</t>
-  </si>
-  <si>
-    <t>retourner</t>
-  </si>
-  <si>
-    <t>Level.DisplayName1</t>
-  </si>
-  <si>
-    <t>Niveau 1 Nom</t>
-  </si>
-  <si>
-    <t>Level.DisplayName2</t>
-  </si>
-  <si>
-    <t>Niveau 2 Nom</t>
-  </si>
-  <si>
-    <t>Level.DisplayName3</t>
-  </si>
-  <si>
-    <t>Niveau 3 nom</t>
-  </si>
-  <si>
-    <t>Level.DisplayName4</t>
-  </si>
-  <si>
-    <t>Niveau 4 nom</t>
-  </si>
-  <si>
-    <t>Level.DisplayName5</t>
-  </si>
-  <si>
-    <t>Niveau 5 nom</t>
-  </si>
-  <si>
-    <t>MenuUIForm.Tips</t>
-  </si>
-  <si>
-    <t>Cliquez sur Démarrer</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+  <si>
+    <t>NoSaveData</t>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>Nothing</t>
@@ -135,34 +81,10 @@
     <t>Ouvrir</t>
   </si>
   <si>
-    <t>RatingDialog.CancelTxt</t>
-  </si>
-  <si>
-    <t>Annuler</t>
-  </si>
-  <si>
-    <t>RatingDialog.Description</t>
-  </si>
-  <si>
-    <t>Vous aimez ce jeu? \ n Veuillez donner 5 étoiles!</t>
-  </si>
-  <si>
-    <t>RatingDialog.HighRatingTips</t>
-  </si>
-  <si>
-    <t>Merci pour l'affirmation! Nous allons construire!</t>
-  </si>
-  <si>
-    <t>RatingDialog.LowRatingTips</t>
-  </si>
-  <si>
-    <t>Merci pour votre évaluation, nous essayons d'affiner l'optimisation!</t>
-  </si>
-  <si>
-    <t>RatingDialog.RateTxt</t>
-  </si>
-  <si>
-    <t>Étoile de commentaire</t>
+    <t>OpenSaveList</t>
+  </si>
+  <si>
+    <t>Ouvrir la liste de sauvegarde</t>
   </si>
   <si>
     <t>Settings.Help</t>
@@ -213,16 +135,10 @@
     <t>Secousses</t>
   </si>
   <si>
-    <t>SHOP</t>
-  </si>
-  <si>
-    <t>magasin</t>
-  </si>
-  <si>
-    <t>STEERING</t>
-  </si>
-  <si>
-    <t>Conduire</t>
+    <t>Story_Welcome</t>
+  </si>
+  <si>
+    <t>Bienvenue dans le monde de la bataille des dieux. Ici, vous incarnerez un héros dans un voyage épique et aventureux. Prêt à commencer votre saga?</t>
   </si>
   <si>
     <t>TermsOfService</t>
@@ -231,16 +147,28 @@
     <t>Conditions de service</t>
   </si>
   <si>
-    <t>UNLOCK</t>
-  </si>
-  <si>
-    <t>déverrouiller</t>
-  </si>
-  <si>
-    <t>Victory</t>
-  </si>
-  <si>
-    <t>La victoire du jeu</t>
+    <t>UI_Continue</t>
+  </si>
+  <si>
+    <t>Continuer</t>
+  </si>
+  <si>
+    <t>UI_InputName</t>
+  </si>
+  <si>
+    <t>Veuillez entrer votre prénom</t>
+  </si>
+  <si>
+    <t>UI_PressSpace</t>
+  </si>
+  <si>
+    <t>Appuyez sur espace pour continuer</t>
+  </si>
+  <si>
+    <t>UI_Welcome</t>
+  </si>
+  <si>
+    <t>Bienvenue à vous, {0}!</t>
   </si>
 </sst>
 </file>
@@ -308,7 +236,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp14.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp15.xml><?xml version="1.0" encoding="utf-8"?>
@@ -316,7 +244,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp16.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp17.xml><?xml version="1.0" encoding="utf-8"?>
@@ -324,7 +252,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp18.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp19.xml><?xml version="1.0" encoding="utf-8"?>
@@ -335,55 +263,7 @@
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
-<file path=xl/ctrlProps/ctrlProp20.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp21.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp22.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp23.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp24.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp25.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp26.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp27.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp28.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp29.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
 <file path=xl/ctrlProps/ctrlProp3.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp30.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp31.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
@@ -538,6 +418,794 @@
     <mc:Fallback/>
   </mc:AlternateContent>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
@@ -554,10 +1222,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A1" id="1056">
+            <xdr:cNvPr hidden="1" name="A1" id="1044">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1056"/>
+                  <a14:compatExt spid="_x0000_s1044"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -640,10 +1308,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A2" id="1057">
+            <xdr:cNvPr hidden="1" name="A2" id="1045">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1057"/>
+                  <a14:compatExt spid="_x0000_s1045"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -726,10 +1394,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A3" id="1058">
+            <xdr:cNvPr hidden="1" name="A3" id="1046">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1058"/>
+                  <a14:compatExt spid="_x0000_s1046"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -812,10 +1480,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A4" id="1059">
+            <xdr:cNvPr hidden="1" name="A4" id="1047">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1059"/>
+                  <a14:compatExt spid="_x0000_s1047"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -898,10 +1566,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A5" id="1060">
+            <xdr:cNvPr hidden="1" name="A5" id="1048">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1060"/>
+                  <a14:compatExt spid="_x0000_s1048"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -984,10 +1652,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A6" id="1061">
+            <xdr:cNvPr hidden="1" name="A6" id="1049">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1061"/>
+                  <a14:compatExt spid="_x0000_s1049"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -1070,10 +1738,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A7" id="1062">
+            <xdr:cNvPr hidden="1" name="A7" id="1050">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1062"/>
+                  <a14:compatExt spid="_x0000_s1050"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -1156,10 +1824,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A8" id="1063">
+            <xdr:cNvPr hidden="1" name="A8" id="1051">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1063"/>
+                  <a14:compatExt spid="_x0000_s1051"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -1242,10 +1910,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A9" id="1064">
+            <xdr:cNvPr hidden="1" name="A9" id="1052">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1064"/>
+                  <a14:compatExt spid="_x0000_s1052"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -1328,10 +1996,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A10" id="1065">
+            <xdr:cNvPr hidden="1" name="A10" id="1053">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1065"/>
+                  <a14:compatExt spid="_x0000_s1053"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -1414,10 +2082,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A11" id="1066">
+            <xdr:cNvPr hidden="1" name="A11" id="1054">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1066"/>
+                  <a14:compatExt spid="_x0000_s1054"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -1500,10 +2168,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A12" id="1067">
+            <xdr:cNvPr hidden="1" name="A12" id="1055">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1067"/>
+                  <a14:compatExt spid="_x0000_s1055"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -1586,10 +2254,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A13" id="1068">
+            <xdr:cNvPr hidden="1" name="A13" id="1056">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1068"/>
+                  <a14:compatExt spid="_x0000_s1056"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -1672,10 +2340,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A14" id="1069">
+            <xdr:cNvPr hidden="1" name="A14" id="1057">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1069"/>
+                  <a14:compatExt spid="_x0000_s1057"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -1758,10 +2426,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A15" id="1070">
+            <xdr:cNvPr hidden="1" name="A15" id="1058">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1070"/>
+                  <a14:compatExt spid="_x0000_s1058"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -1844,10 +2512,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A16" id="1071">
+            <xdr:cNvPr hidden="1" name="A16" id="1059">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1071"/>
+                  <a14:compatExt spid="_x0000_s1059"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -1930,10 +2598,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A17" id="1072">
+            <xdr:cNvPr hidden="1" name="A17" id="1060">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1072"/>
+                  <a14:compatExt spid="_x0000_s1060"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -2016,10 +2684,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A18" id="1073">
+            <xdr:cNvPr hidden="1" name="A18" id="1061">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1073"/>
+                  <a14:compatExt spid="_x0000_s1061"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -2102,10 +2770,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A19" id="1074">
+            <xdr:cNvPr hidden="1" name="A19" id="1062">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1074"/>
+                  <a14:compatExt spid="_x0000_s1062"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -2171,1048 +2839,16 @@
     </mc:Choice>
     <mc:Fallback/>
   </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>19</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>20</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A20" id="1075">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1075"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>20</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>21</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A21" id="1076">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1076"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>21</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>22</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A22" id="1077">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1077"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>22</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>23</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A23" id="1078">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1078"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>23</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>24</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A24" id="1079">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1079"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>24</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>25</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A25" id="1080">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1080"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>25</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>26</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A26" id="1081">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1081"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>26</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>27</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A27" id="1082">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1082"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>27</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>28</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A28" id="1083">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1083"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>28</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>29</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A29" id="1084">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1084"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>29</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>30</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A30" id="1085">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1085"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>30</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>31</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A31" id="1086">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1086"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
 </xdr:wsDr>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.140625" customWidth="1"/>
-    <col min="2" max="2" width="25.4074859619141" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="50" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3385,114 +3021,6 @@
       </c>
       <c r="C19" s="0" t="s">
         <v>37</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1"/>
-      <c r="B20" s="0" t="s">
-        <v>38</v>
-      </c>
-      <c r="C20" s="0" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1"/>
-      <c r="B21" s="0" t="s">
-        <v>40</v>
-      </c>
-      <c r="C21" s="0" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1"/>
-      <c r="B22" s="0" t="s">
-        <v>42</v>
-      </c>
-      <c r="C22" s="0" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1"/>
-      <c r="B23" s="0" t="s">
-        <v>44</v>
-      </c>
-      <c r="C23" s="0" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1"/>
-      <c r="B24" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="C24" s="0" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1"/>
-      <c r="B25" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="C25" s="0" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1"/>
-      <c r="B26" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="C26" s="0" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1"/>
-      <c r="B27" s="0" t="s">
-        <v>52</v>
-      </c>
-      <c r="C27" s="0" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1"/>
-      <c r="B28" s="0" t="s">
-        <v>54</v>
-      </c>
-      <c r="C28" s="0" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1"/>
-      <c r="B29" s="0" t="s">
-        <v>56</v>
-      </c>
-      <c r="C29" s="0" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1"/>
-      <c r="B30" s="0" t="s">
-        <v>58</v>
-      </c>
-      <c r="C30" s="0" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1"/>
-      <c r="B31" s="0" t="s">
-        <v>60</v>
-      </c>
-      <c r="C31" s="0" t="s">
-        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -3504,7 +3032,7 @@
       <controls xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1056" r:id="rId35" name="A1">
+            <control shapeId="1044" r:id="rId221" name="A1">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -3526,7 +3054,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1057" r:id="rId36" name="A2">
+            <control shapeId="1045" r:id="rId222" name="A2">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -3548,7 +3076,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1058" r:id="rId37" name="A3">
+            <control shapeId="1046" r:id="rId223" name="A3">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -3570,7 +3098,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1059" r:id="rId38" name="A4">
+            <control shapeId="1047" r:id="rId224" name="A4">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -3592,7 +3120,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1060" r:id="rId39" name="A5">
+            <control shapeId="1048" r:id="rId225" name="A5">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -3614,7 +3142,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1061" r:id="rId40" name="A6">
+            <control shapeId="1049" r:id="rId226" name="A6">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -3636,7 +3164,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1062" r:id="rId41" name="A7">
+            <control shapeId="1050" r:id="rId227" name="A7">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -3658,7 +3186,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1063" r:id="rId42" name="A8">
+            <control shapeId="1051" r:id="rId228" name="A8">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -3680,7 +3208,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1064" r:id="rId43" name="A9">
+            <control shapeId="1052" r:id="rId229" name="A9">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -3702,7 +3230,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1065" r:id="rId44" name="A10">
+            <control shapeId="1053" r:id="rId230" name="A10">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -3724,7 +3252,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1066" r:id="rId45" name="A11">
+            <control shapeId="1054" r:id="rId231" name="A11">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -3746,7 +3274,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1067" r:id="rId46" name="A12">
+            <control shapeId="1055" r:id="rId232" name="A12">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -3768,7 +3296,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1068" r:id="rId47" name="A13">
+            <control shapeId="1056" r:id="rId233" name="A13">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -3790,7 +3318,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1069" r:id="rId48" name="A14">
+            <control shapeId="1057" r:id="rId234" name="A14">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -3812,7 +3340,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1070" r:id="rId49" name="A15">
+            <control shapeId="1058" r:id="rId235" name="A15">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -3834,7 +3362,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1071" r:id="rId50" name="A16">
+            <control shapeId="1059" r:id="rId236" name="A16">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -3856,7 +3384,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1072" r:id="rId51" name="A17">
+            <control shapeId="1060" r:id="rId237" name="A17">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -3878,7 +3406,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1073" r:id="rId52" name="A18">
+            <control shapeId="1061" r:id="rId238" name="A18">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -3900,7 +3428,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1074" r:id="rId53" name="A19">
+            <control shapeId="1062" r:id="rId239" name="A19">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -3913,270 +3441,6 @@
                     <xdr:col>0</xdr:col>
                     <xdr:colOff>285750</xdr:colOff>
                     <xdr:row>19</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1075" r:id="rId54" name="A20">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>19</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>20</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1076" r:id="rId55" name="A21">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>20</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>21</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1077" r:id="rId56" name="A22">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>21</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>22</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1078" r:id="rId57" name="A23">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>22</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>23</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1079" r:id="rId58" name="A24">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>23</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>24</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1080" r:id="rId59" name="A25">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>24</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>25</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1081" r:id="rId60" name="A26">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>25</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>26</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1082" r:id="rId61" name="A27">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>26</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>27</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1083" r:id="rId62" name="A28">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>27</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>28</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1084" r:id="rId63" name="A29">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>28</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>29</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1085" r:id="rId64" name="A30">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>29</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>30</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1086" r:id="rId65" name="A31">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>30</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>31</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </to>
                 </anchor>

--- a/AAAGameData/Languages/French.xlsx
+++ b/AAAGameData/Languages/French.xlsx
@@ -55,12 +55,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
   <si>
     <t>NoSaveData</t>
   </si>
   <si>
-    <t/>
+    <t>Pas de données archivées</t>
   </si>
   <si>
     <t>Nothing</t>
@@ -85,6 +85,30 @@
   </si>
   <si>
     <t>Ouvrir la liste de sauvegarde</t>
+  </si>
+  <si>
+    <t>scene.base.name</t>
+  </si>
+  <si>
+    <t>Base</t>
+  </si>
+  <si>
+    <t>scene.menu.name</t>
+  </si>
+  <si>
+    <t>Menu principal</t>
+  </si>
+  <si>
+    <t>scene.tutorial.name</t>
+  </si>
+  <si>
+    <t>Un certain laboratoire</t>
+  </si>
+  <si>
+    <t>scene.world.name</t>
+  </si>
+  <si>
+    <t>Le grand monde</t>
   </si>
   <si>
     <t>Settings.Help</t>
@@ -114,7 +138,7 @@
     <t>Settings.Rating</t>
   </si>
   <si>
-    <t>Score</t>
+    <t>notation</t>
   </si>
   <si>
     <t>Settings.SFX</t>
@@ -132,7 +156,7 @@
     <t>Settings.Vibrate</t>
   </si>
   <si>
-    <t>Secousses</t>
+    <t>vibration</t>
   </si>
   <si>
     <t>Story_Welcome</t>
@@ -150,7 +174,7 @@
     <t>UI_Continue</t>
   </si>
   <si>
-    <t>Continuer</t>
+    <t>continuer</t>
   </si>
   <si>
     <t>UI_InputName</t>
@@ -168,7 +192,7 @@
     <t>UI_Welcome</t>
   </si>
   <si>
-    <t>Bienvenue à vous, {0}!</t>
+    <t>Bienvenue à vous</t>
   </si>
 </sst>
 </file>
@@ -236,7 +260,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp14.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp15.xml><?xml version="1.0" encoding="utf-8"?>
@@ -244,7 +268,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp16.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp17.xml><?xml version="1.0" encoding="utf-8"?>
@@ -260,6 +284,22 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp2.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp20.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp21.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp22.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp23.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
@@ -1206,6 +1246,634 @@
     <mc:Fallback/>
   </mc:AlternateContent>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
@@ -1222,351 +1890,7 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A1" id="1044">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1044"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>1</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>2</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A2" id="1045">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1045"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>2</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>3</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A3" id="1046">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1046"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>3</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>4</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A4" id="1047">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1047"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>4</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>5</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A5" id="1048">
+            <xdr:cNvPr hidden="1" name="A1" id="1048">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1048"/>
@@ -1641,18 +1965,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>5</xdr:row>
+          <xdr:row>1</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>6</xdr:row>
+          <xdr:row>2</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A6" id="1049">
+            <xdr:cNvPr hidden="1" name="A2" id="1049">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1049"/>
@@ -1727,18 +2051,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>6</xdr:row>
+          <xdr:row>2</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>7</xdr:row>
+          <xdr:row>3</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A7" id="1050">
+            <xdr:cNvPr hidden="1" name="A3" id="1050">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1050"/>
@@ -1813,18 +2137,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>7</xdr:row>
+          <xdr:row>3</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>8</xdr:row>
+          <xdr:row>4</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A8" id="1051">
+            <xdr:cNvPr hidden="1" name="A4" id="1051">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1051"/>
@@ -1899,18 +2223,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>8</xdr:row>
+          <xdr:row>4</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>9</xdr:row>
+          <xdr:row>5</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A9" id="1052">
+            <xdr:cNvPr hidden="1" name="A5" id="1052">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1052"/>
@@ -1985,18 +2309,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>9</xdr:row>
+          <xdr:row>5</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>10</xdr:row>
+          <xdr:row>6</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A10" id="1053">
+            <xdr:cNvPr hidden="1" name="A6" id="1053">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1053"/>
@@ -2071,18 +2395,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>10</xdr:row>
+          <xdr:row>6</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>11</xdr:row>
+          <xdr:row>7</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A11" id="1054">
+            <xdr:cNvPr hidden="1" name="A7" id="1054">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1054"/>
@@ -2157,18 +2481,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>11</xdr:row>
+          <xdr:row>7</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>12</xdr:row>
+          <xdr:row>8</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A12" id="1055">
+            <xdr:cNvPr hidden="1" name="A8" id="1055">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1055"/>
@@ -2243,18 +2567,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>12</xdr:row>
+          <xdr:row>8</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>13</xdr:row>
+          <xdr:row>9</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A13" id="1056">
+            <xdr:cNvPr hidden="1" name="A9" id="1056">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1056"/>
@@ -2329,18 +2653,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>13</xdr:row>
+          <xdr:row>9</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>14</xdr:row>
+          <xdr:row>10</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A14" id="1057">
+            <xdr:cNvPr hidden="1" name="A10" id="1057">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1057"/>
@@ -2415,18 +2739,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>14</xdr:row>
+          <xdr:row>10</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>15</xdr:row>
+          <xdr:row>11</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A15" id="1058">
+            <xdr:cNvPr hidden="1" name="A11" id="1058">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1058"/>
@@ -2501,18 +2825,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>15</xdr:row>
+          <xdr:row>11</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>16</xdr:row>
+          <xdr:row>12</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A16" id="1059">
+            <xdr:cNvPr hidden="1" name="A12" id="1059">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1059"/>
@@ -2587,18 +2911,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>16</xdr:row>
+          <xdr:row>12</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>17</xdr:row>
+          <xdr:row>13</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A17" id="1060">
+            <xdr:cNvPr hidden="1" name="A13" id="1060">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1060"/>
@@ -2673,18 +2997,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>17</xdr:row>
+          <xdr:row>13</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>18</xdr:row>
+          <xdr:row>14</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A18" id="1061">
+            <xdr:cNvPr hidden="1" name="A14" id="1061">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1061"/>
@@ -2759,18 +3083,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>18</xdr:row>
+          <xdr:row>14</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>19</xdr:row>
+          <xdr:row>15</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A19" id="1062">
+            <xdr:cNvPr hidden="1" name="A15" id="1062">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1062"/>
@@ -2839,12 +3163,700 @@
     </mc:Choice>
     <mc:Fallback/>
   </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>15</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>16</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A16" id="1063">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1063"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>16</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>17</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A17" id="1064">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1064"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>17</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>18</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A18" id="1065">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1065"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>18</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>19</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A19" id="1066">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1066"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>19</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>20</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A20" id="1067">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1067"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>20</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>21</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A21" id="1068">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1068"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>21</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>22</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A22" id="1069">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1069"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>22</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>23</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A23" id="1070">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1070"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
 </xdr:wsDr>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.140625" customWidth="1"/>
@@ -3023,6 +4035,42 @@
         <v>37</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="1"/>
+      <c r="B20" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20" s="0" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1"/>
+      <c r="B21" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="C21" s="0" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1"/>
+      <c r="B22" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="C22" s="0" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1"/>
+      <c r="B23" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="C23" s="0" t="s">
+        <v>45</v>
+      </c>
+    </row>
   </sheetData>
   <headerFooter/>
   <drawing r:id="rId1"/>
@@ -3032,7 +4080,7 @@
       <controls xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1044" r:id="rId221" name="A1">
+            <control shapeId="1048" r:id="rId371" name="A1">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -3054,7 +4102,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1045" r:id="rId222" name="A2">
+            <control shapeId="1049" r:id="rId372" name="A2">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -3076,7 +4124,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1046" r:id="rId223" name="A3">
+            <control shapeId="1050" r:id="rId373" name="A3">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -3098,7 +4146,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1047" r:id="rId224" name="A4">
+            <control shapeId="1051" r:id="rId374" name="A4">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -3120,7 +4168,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1048" r:id="rId225" name="A5">
+            <control shapeId="1052" r:id="rId375" name="A5">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -3142,7 +4190,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1049" r:id="rId226" name="A6">
+            <control shapeId="1053" r:id="rId376" name="A6">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -3164,7 +4212,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1050" r:id="rId227" name="A7">
+            <control shapeId="1054" r:id="rId377" name="A7">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -3186,7 +4234,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1051" r:id="rId228" name="A8">
+            <control shapeId="1055" r:id="rId378" name="A8">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -3208,7 +4256,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1052" r:id="rId229" name="A9">
+            <control shapeId="1056" r:id="rId379" name="A9">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -3230,7 +4278,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1053" r:id="rId230" name="A10">
+            <control shapeId="1057" r:id="rId380" name="A10">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -3252,7 +4300,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1054" r:id="rId231" name="A11">
+            <control shapeId="1058" r:id="rId381" name="A11">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -3274,7 +4322,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1055" r:id="rId232" name="A12">
+            <control shapeId="1059" r:id="rId382" name="A12">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -3296,7 +4344,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1056" r:id="rId233" name="A13">
+            <control shapeId="1060" r:id="rId383" name="A13">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -3318,7 +4366,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1057" r:id="rId234" name="A14">
+            <control shapeId="1061" r:id="rId384" name="A14">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -3340,7 +4388,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1058" r:id="rId235" name="A15">
+            <control shapeId="1062" r:id="rId385" name="A15">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -3362,7 +4410,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1059" r:id="rId236" name="A16">
+            <control shapeId="1063" r:id="rId386" name="A16">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -3384,7 +4432,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1060" r:id="rId237" name="A17">
+            <control shapeId="1064" r:id="rId387" name="A17">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -3406,7 +4454,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1061" r:id="rId238" name="A18">
+            <control shapeId="1065" r:id="rId388" name="A18">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -3428,7 +4476,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1062" r:id="rId239" name="A19">
+            <control shapeId="1066" r:id="rId389" name="A19">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -3448,6 +4496,94 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1067" r:id="rId390" name="A20">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>19</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>20</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1068" r:id="rId391" name="A21">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>20</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>21</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1069" r:id="rId392" name="A22">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>21</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>22</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1070" r:id="rId393" name="A23">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>22</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>23</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
       </controls>
     </Choice>
   </AlternateContent>

--- a/AAAGameData/Languages/French.xlsx
+++ b/AAAGameData/Languages/French.xlsx
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
   <si>
     <t>NoSaveData</t>
   </si>
@@ -87,16 +87,58 @@
     <t>Ouvrir la liste de sauvegarde</t>
   </si>
   <si>
+    <t>scene.abyss.name</t>
+  </si>
+  <si>
+    <t>Terre des abysses</t>
+  </si>
+  <si>
+    <t>scene.avalon.name</t>
+  </si>
+  <si>
+    <t>Avalon</t>
+  </si>
+  <si>
+    <t>scene.babylon.name</t>
+  </si>
+  <si>
+    <t>Jardin aérien de Babylone</t>
+  </si>
+  <si>
     <t>scene.base.name</t>
   </si>
   <si>
     <t>Base</t>
   </si>
   <si>
+    <t>scene.herheim.name</t>
+  </si>
+  <si>
+    <t>Herheimer</t>
+  </si>
+  <si>
     <t>scene.menu.name</t>
   </si>
   <si>
     <t>Menu principal</t>
+  </si>
+  <si>
+    <t>scene.olympus.name</t>
+  </si>
+  <si>
+    <t>Le Mont Olympe</t>
+  </si>
+  <si>
+    <t>scene.takamahara.name</t>
+  </si>
+  <si>
+    <t>Le haut ciel</t>
+  </si>
+  <si>
+    <t>scene.tiangong.name</t>
+  </si>
+  <si>
+    <t>Palais céleste</t>
   </si>
   <si>
     <t>scene.tutorial.name</t>
@@ -244,7 +286,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp10.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp11.xml><?xml version="1.0" encoding="utf-8"?>
@@ -252,15 +294,15 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp12.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp13.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp14.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp15.xml><?xml version="1.0" encoding="utf-8"?>
@@ -276,7 +318,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp18.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp19.xml><?xml version="1.0" encoding="utf-8"?>
@@ -288,7 +330,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp20.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp21.xml><?xml version="1.0" encoding="utf-8"?>
@@ -296,14 +338,42 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp22.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp23.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
+<file path=xl/ctrlProps/ctrlProp24.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp25.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp26.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp27.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp28.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp29.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+</file>
+
 <file path=xl/ctrlProps/ctrlProp3.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp30.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
@@ -316,15 +386,15 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp6.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp7.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp8.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp9.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1874,6 +1944,338 @@
     <mc:Fallback/>
   </mc:AlternateContent>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
@@ -1890,10 +2292,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A1" id="1048">
+            <xdr:cNvPr hidden="1" name="A1" id="1055">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1048"/>
+                  <a14:compatExt spid="_x0000_s1055"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -1976,10 +2378,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A2" id="1049">
+            <xdr:cNvPr hidden="1" name="A2" id="1056">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1049"/>
+                  <a14:compatExt spid="_x0000_s1056"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -2062,10 +2464,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A3" id="1050">
+            <xdr:cNvPr hidden="1" name="A3" id="1057">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1050"/>
+                  <a14:compatExt spid="_x0000_s1057"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -2148,10 +2550,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A4" id="1051">
+            <xdr:cNvPr hidden="1" name="A4" id="1058">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1051"/>
+                  <a14:compatExt spid="_x0000_s1058"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -2234,10 +2636,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A5" id="1052">
+            <xdr:cNvPr hidden="1" name="A5" id="1059">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1052"/>
+                  <a14:compatExt spid="_x0000_s1059"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -2320,10 +2722,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A6" id="1053">
+            <xdr:cNvPr hidden="1" name="A6" id="1060">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1053"/>
+                  <a14:compatExt spid="_x0000_s1060"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -2406,10 +2808,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A7" id="1054">
+            <xdr:cNvPr hidden="1" name="A7" id="1061">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1054"/>
+                  <a14:compatExt spid="_x0000_s1061"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -2492,10 +2894,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A8" id="1055">
+            <xdr:cNvPr hidden="1" name="A8" id="1062">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1055"/>
+                  <a14:compatExt spid="_x0000_s1062"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -2578,10 +2980,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A9" id="1056">
+            <xdr:cNvPr hidden="1" name="A9" id="1063">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1056"/>
+                  <a14:compatExt spid="_x0000_s1063"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -2664,10 +3066,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A10" id="1057">
+            <xdr:cNvPr hidden="1" name="A10" id="1064">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1057"/>
+                  <a14:compatExt spid="_x0000_s1064"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -2750,10 +3152,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A11" id="1058">
+            <xdr:cNvPr hidden="1" name="A11" id="1065">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1058"/>
+                  <a14:compatExt spid="_x0000_s1065"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -2836,10 +3238,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A12" id="1059">
+            <xdr:cNvPr hidden="1" name="A12" id="1066">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1059"/>
+                  <a14:compatExt spid="_x0000_s1066"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -2922,10 +3324,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A13" id="1060">
+            <xdr:cNvPr hidden="1" name="A13" id="1067">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1060"/>
+                  <a14:compatExt spid="_x0000_s1067"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -3008,10 +3410,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A14" id="1061">
+            <xdr:cNvPr hidden="1" name="A14" id="1068">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1061"/>
+                  <a14:compatExt spid="_x0000_s1068"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -3094,10 +3496,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A15" id="1062">
+            <xdr:cNvPr hidden="1" name="A15" id="1069">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1062"/>
+                  <a14:compatExt spid="_x0000_s1069"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -3180,10 +3582,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A16" id="1063">
+            <xdr:cNvPr hidden="1" name="A16" id="1070">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1063"/>
+                  <a14:compatExt spid="_x0000_s1070"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -3266,10 +3668,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A17" id="1064">
+            <xdr:cNvPr hidden="1" name="A17" id="1071">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1064"/>
+                  <a14:compatExt spid="_x0000_s1071"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -3352,10 +3754,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A18" id="1065">
+            <xdr:cNvPr hidden="1" name="A18" id="1072">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1065"/>
+                  <a14:compatExt spid="_x0000_s1072"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -3438,10 +3840,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A19" id="1066">
+            <xdr:cNvPr hidden="1" name="A19" id="1073">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1066"/>
+                  <a14:compatExt spid="_x0000_s1073"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -3524,10 +3926,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A20" id="1067">
+            <xdr:cNvPr hidden="1" name="A20" id="1074">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1067"/>
+                  <a14:compatExt spid="_x0000_s1074"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -3610,10 +4012,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A21" id="1068">
+            <xdr:cNvPr hidden="1" name="A21" id="1075">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1068"/>
+                  <a14:compatExt spid="_x0000_s1075"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -3696,10 +4098,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A22" id="1069">
+            <xdr:cNvPr hidden="1" name="A22" id="1076">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1069"/>
+                  <a14:compatExt spid="_x0000_s1076"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -3782,10 +4184,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A23" id="1070">
+            <xdr:cNvPr hidden="1" name="A23" id="1077">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1070"/>
+                  <a14:compatExt spid="_x0000_s1077"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -3851,16 +4253,618 @@
     </mc:Choice>
     <mc:Fallback/>
   </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>23</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>24</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A24" id="1078">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1078"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>24</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>25</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A25" id="1079">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1079"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>25</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>26</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A26" id="1080">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1080"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>26</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>27</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A27" id="1081">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1081"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>27</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>28</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A28" id="1082">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1082"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>28</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>29</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A29" id="1083">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1083"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>29</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>30</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A30" id="1084">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1084"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
 </xdr:wsDr>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.140625" customWidth="1"/>
-    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="2" max="2" width="22.2728118896484" customWidth="1"/>
     <col min="3" max="3" width="50" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4069,6 +5073,69 @@
       </c>
       <c r="C23" s="0" t="s">
         <v>45</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1"/>
+      <c r="B24" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="C24" s="0" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1"/>
+      <c r="B25" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="C25" s="0" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1"/>
+      <c r="B26" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="C26" s="0" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1"/>
+      <c r="B27" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="C27" s="0" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1"/>
+      <c r="B28" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="C28" s="0" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1"/>
+      <c r="B29" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C29" s="0" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1"/>
+      <c r="B30" s="0" t="s">
+        <v>58</v>
+      </c>
+      <c r="C30" s="0" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -4080,7 +5147,7 @@
       <controls xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1048" r:id="rId371" name="A1">
+            <control shapeId="1055" r:id="rId451" name="A1">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4102,7 +5169,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1049" r:id="rId372" name="A2">
+            <control shapeId="1056" r:id="rId452" name="A2">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4124,7 +5191,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1050" r:id="rId373" name="A3">
+            <control shapeId="1057" r:id="rId453" name="A3">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4146,7 +5213,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1051" r:id="rId374" name="A4">
+            <control shapeId="1058" r:id="rId454" name="A4">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4168,7 +5235,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1052" r:id="rId375" name="A5">
+            <control shapeId="1059" r:id="rId455" name="A5">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4190,7 +5257,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1053" r:id="rId376" name="A6">
+            <control shapeId="1060" r:id="rId456" name="A6">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4212,7 +5279,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1054" r:id="rId377" name="A7">
+            <control shapeId="1061" r:id="rId457" name="A7">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4234,7 +5301,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1055" r:id="rId378" name="A8">
+            <control shapeId="1062" r:id="rId458" name="A8">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4256,7 +5323,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1056" r:id="rId379" name="A9">
+            <control shapeId="1063" r:id="rId459" name="A9">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4278,7 +5345,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1057" r:id="rId380" name="A10">
+            <control shapeId="1064" r:id="rId460" name="A10">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4300,7 +5367,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1058" r:id="rId381" name="A11">
+            <control shapeId="1065" r:id="rId461" name="A11">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4322,7 +5389,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1059" r:id="rId382" name="A12">
+            <control shapeId="1066" r:id="rId462" name="A12">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4344,7 +5411,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1060" r:id="rId383" name="A13">
+            <control shapeId="1067" r:id="rId463" name="A13">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4366,7 +5433,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1061" r:id="rId384" name="A14">
+            <control shapeId="1068" r:id="rId464" name="A14">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4388,7 +5455,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1062" r:id="rId385" name="A15">
+            <control shapeId="1069" r:id="rId465" name="A15">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4410,7 +5477,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1063" r:id="rId386" name="A16">
+            <control shapeId="1070" r:id="rId466" name="A16">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4432,7 +5499,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1064" r:id="rId387" name="A17">
+            <control shapeId="1071" r:id="rId467" name="A17">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4454,7 +5521,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1065" r:id="rId388" name="A18">
+            <control shapeId="1072" r:id="rId468" name="A18">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4476,7 +5543,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1066" r:id="rId389" name="A19">
+            <control shapeId="1073" r:id="rId469" name="A19">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4498,7 +5565,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1067" r:id="rId390" name="A20">
+            <control shapeId="1074" r:id="rId470" name="A20">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4520,7 +5587,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1068" r:id="rId391" name="A21">
+            <control shapeId="1075" r:id="rId471" name="A21">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4542,7 +5609,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1069" r:id="rId392" name="A22">
+            <control shapeId="1076" r:id="rId472" name="A22">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4564,7 +5631,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1070" r:id="rId393" name="A23">
+            <control shapeId="1077" r:id="rId473" name="A23">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4577,6 +5644,160 @@
                     <xdr:col>0</xdr:col>
                     <xdr:colOff>285750</xdr:colOff>
                     <xdr:row>23</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1078" r:id="rId474" name="A24">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>23</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>24</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1079" r:id="rId475" name="A25">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>24</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>25</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1080" r:id="rId476" name="A26">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>25</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>26</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1081" r:id="rId477" name="A27">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>26</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>27</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1082" r:id="rId478" name="A28">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>27</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>28</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1083" r:id="rId479" name="A29">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>28</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>29</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1084" r:id="rId480" name="A30">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>29</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>30</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </to>
                 </anchor>
